--- a/Behind/july 2026/Daily Reports/Lahore LMT.xlsx
+++ b/Behind/july 2026/Daily Reports/Lahore LMT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097977FF-18C6-4D19-AEC5-1D07BCB8B460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53CB97C-B19F-4D34-B3BD-F827CF3C0D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,13 +61,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Marchandiser Route'!$A$2:$K$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Shabir!$A$2:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UploadBeat-Pak'!$B$1:$J$602</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Elite LMT Sales Update'!$A$1:$H$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4531" uniqueCount="1539">
   <si>
     <t>Customer Name</t>
   </si>
@@ -4152,21 +4153,6 @@
     <t>PPL0099</t>
   </si>
   <si>
-    <t>PPL0100</t>
-  </si>
-  <si>
-    <t>PPL0101</t>
-  </si>
-  <si>
-    <t>PPL0102</t>
-  </si>
-  <si>
-    <t>PPL0103</t>
-  </si>
-  <si>
-    <t>PPL0104</t>
-  </si>
-  <si>
     <t>PPL0105</t>
   </si>
   <si>
@@ -4332,9 +4318,6 @@
     <t>Vip</t>
   </si>
   <si>
-    <t xml:space="preserve">Umaima </t>
-  </si>
-  <si>
     <t>Raheem Store</t>
   </si>
   <si>
@@ -4347,21 +4330,12 @@
     <t xml:space="preserve">Rainbow </t>
   </si>
   <si>
-    <t xml:space="preserve">Decent </t>
-  </si>
-  <si>
-    <t>Rainbiw</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jalal Sons </t>
   </si>
   <si>
     <t xml:space="preserve">Zohra Mart </t>
   </si>
   <si>
-    <t xml:space="preserve">Al Rehmat </t>
-  </si>
-  <si>
     <t xml:space="preserve">Raheem Store </t>
   </si>
   <si>
@@ -4371,57 +4345,18 @@
     <t>Naimat Khana</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagina </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hotpot Souces </t>
-  </si>
-  <si>
     <t>Family Store</t>
   </si>
   <si>
-    <t>Shahwar Mega Mart</t>
-  </si>
-  <si>
-    <t>Easy Mart</t>
-  </si>
-  <si>
-    <t>Sana C &amp; C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al Fateh </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raheem </t>
-  </si>
-  <si>
-    <t>Jalal Sons warehouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raja Sab </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Askari </t>
-  </si>
-  <si>
     <t xml:space="preserve">Rubaika </t>
   </si>
   <si>
-    <t>Swera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Euro NFC </t>
   </si>
   <si>
     <t>Jalal Sons</t>
   </si>
   <si>
-    <t xml:space="preserve">Zubaida Traders </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nabeel Traders </t>
-  </si>
-  <si>
     <t>Euro K-2</t>
   </si>
   <si>
@@ -4434,21 +4369,6 @@
     <t xml:space="preserve">HA Mart </t>
   </si>
   <si>
-    <t>Naqshbandi Indocaion free</t>
-  </si>
-  <si>
-    <t>Naqshbandi</t>
-  </si>
-  <si>
-    <t>Aster Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usman Canvenioun </t>
-  </si>
-  <si>
-    <t>Manawan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Shadbagh </t>
   </si>
   <si>
@@ -4458,103 +4378,313 @@
     <t xml:space="preserve">Model Town </t>
   </si>
   <si>
-    <t>Shadra Town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muredky </t>
-  </si>
-  <si>
     <t xml:space="preserve">Johar Town </t>
   </si>
   <si>
     <t xml:space="preserve">Wapda Town </t>
   </si>
   <si>
-    <t>Izmir Town</t>
-  </si>
-  <si>
-    <t>Thoker niaz Baig</t>
-  </si>
-  <si>
     <t>EME</t>
   </si>
   <si>
     <t>Mughalpura</t>
   </si>
   <si>
-    <t xml:space="preserve">Al noor Town </t>
-  </si>
-  <si>
     <t>Behria Orchard</t>
   </si>
   <si>
-    <t xml:space="preserve">Nespark Society </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raheem Garden </t>
-  </si>
-  <si>
-    <t>warehouse</t>
-  </si>
-  <si>
     <t>Shaikhupura</t>
   </si>
   <si>
     <t>Gujranwala</t>
   </si>
   <si>
-    <t>Behria Town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">punjab Society </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velencia </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFC </t>
-  </si>
-  <si>
     <t>Askari 11</t>
   </si>
   <si>
-    <t>defence Road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badamibagh </t>
-  </si>
-  <si>
     <t xml:space="preserve">Kareem Park </t>
   </si>
   <si>
     <t>Sabzazaar</t>
   </si>
   <si>
-    <t xml:space="preserve">Sadar </t>
-  </si>
-  <si>
     <t>Head Office</t>
   </si>
   <si>
-    <t xml:space="preserve">Riwand Road Ali Town </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fizaya Society </t>
-  </si>
-  <si>
     <t xml:space="preserve">Jublee Town </t>
   </si>
   <si>
-    <t>Attari darbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shalimar </t>
-  </si>
-  <si>
-    <t>Tajpura</t>
-  </si>
-  <si>
-    <t>LDA Avenue</t>
+    <t>Manawan (Risen)</t>
+  </si>
+  <si>
+    <t>Shadbagh (Risen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umaima  paragon City </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decent Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Wapda Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t>Raheem Store J-Height</t>
+  </si>
+  <si>
+    <t>Al Rehmat</t>
+  </si>
+  <si>
+    <t>Jalal Sons Askari 10</t>
+  </si>
+  <si>
+    <t>Risen Manavan</t>
+  </si>
+  <si>
+    <t>The Hotpot Souces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shehwar Mega Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy Mart </t>
+  </si>
+  <si>
+    <t>Sana Cash &amp; Carry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem  </t>
+  </si>
+  <si>
+    <t>Jalal Sons Warehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raibow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Johar Town </t>
+  </si>
+  <si>
+    <t>Raja Sahb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweera Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders Al Fateh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow C &amp; C </t>
+  </si>
+  <si>
+    <t>Naqshbandi Indoction free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naqshbandi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aster </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usman Canvinain </t>
+  </si>
+  <si>
+    <t>Hafiz Sweets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Main Market </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Lake City </t>
+  </si>
+  <si>
+    <t>Risen Askari 11</t>
+  </si>
+  <si>
+    <t>Risen Thoker Niaz Baig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Shadbagh </t>
+  </si>
+  <si>
+    <t>Risen Al Rehman Garden</t>
+  </si>
+  <si>
+    <t>Shahbaz SB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagina Food </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awan Town </t>
+  </si>
+  <si>
+    <t>Canal view</t>
+  </si>
+  <si>
+    <t>Liyaqat chowk</t>
+  </si>
+  <si>
+    <t>Gulshan Ravi</t>
+  </si>
+  <si>
+    <t>Nadeem Shaheed</t>
+  </si>
+  <si>
+    <t>Poonch Road</t>
+  </si>
+  <si>
+    <t>Rehman pura</t>
+  </si>
+  <si>
+    <t>Rewaz Garden</t>
+  </si>
+  <si>
+    <t>Rustam Park</t>
+  </si>
+  <si>
+    <t>Samanaabd lhr</t>
+  </si>
+  <si>
+    <t>Wahdat Road</t>
+  </si>
+  <si>
+    <t>Kareem Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manawan </t>
+  </si>
+  <si>
+    <t>Model Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WapdaTown </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izmir Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multan Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thokar </t>
+  </si>
+  <si>
+    <t>Raiwind Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canal Road </t>
+  </si>
+  <si>
+    <t>Different</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mughalpura </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manavan </t>
+  </si>
+  <si>
+    <t>Shadra</t>
+  </si>
+  <si>
+    <t>Velencia Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faziya Adda Block </t>
+  </si>
+  <si>
+    <t>Nespak Society Wapda Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatri Chowk </t>
+  </si>
+  <si>
+    <t>Shadara</t>
+  </si>
+  <si>
+    <t>Punjab Society</t>
+  </si>
+  <si>
+    <t>Velencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFC Society </t>
+  </si>
+  <si>
+    <t>Attari Darbar Ferozpur Road</t>
+  </si>
+  <si>
+    <t>Defence Road</t>
+  </si>
+  <si>
+    <t>Rehmat Chowk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badami Bagh </t>
+  </si>
+  <si>
+    <t>Fateh Gher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thoker </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">shadbagh </t>
+  </si>
+  <si>
+    <t>behria Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faisal Town </t>
+  </si>
+  <si>
+    <t>Sahdra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Market </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake City </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niaz Naig </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehman Garden </t>
+  </si>
+  <si>
+    <t>Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al noor town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total </t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>CTN</t>
+  </si>
+  <si>
+    <t>Sampling</t>
   </si>
 </sst>
 </file>
@@ -4847,7 +4977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
@@ -5005,6 +5135,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18571,6 +18703,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{496B225A-0417-44A6-AD52-9103D7FFBD73}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N158"/>
   <sheetFormatPr defaultColWidth="54.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -18579,15 +18714,15 @@
     <col min="3" max="3" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.26953125" style="48" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" style="5" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.453125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="5.453125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.35">
@@ -18655,14 +18790,16 @@
         <v>1262</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="F3" s="44"/>
       <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
+      <c r="H3" s="40">
+        <v>400</v>
+      </c>
       <c r="I3" s="40"/>
       <c r="J3" s="40"/>
       <c r="K3" s="40"/>
@@ -18670,7 +18807,7 @@
       <c r="M3" s="40"/>
       <c r="N3" s="7">
         <f>SUM(G3:M3)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -18685,14 +18822,16 @@
         <v>1263</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>1459</v>
+        <v>1487</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
+      <c r="H4" s="40">
+        <v>400</v>
+      </c>
       <c r="I4" s="40"/>
       <c r="J4" s="40"/>
       <c r="K4" s="40"/>
@@ -18700,7 +18839,7 @@
       <c r="M4" s="40"/>
       <c r="N4" s="7">
         <f t="shared" ref="N4:N67" si="0">SUM(G4:M4)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -18715,14 +18854,16 @@
         <v>1264</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>1460</v>
+        <v>1488</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="H5" s="40">
+        <v>400</v>
+      </c>
       <c r="I5" s="40"/>
       <c r="J5" s="40"/>
       <c r="K5" s="40"/>
@@ -18730,7 +18871,7 @@
       <c r="M5" s="40"/>
       <c r="N5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -18745,14 +18886,16 @@
         <v>1265</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
+      <c r="H6" s="40">
+        <v>280</v>
+      </c>
       <c r="I6" s="40"/>
       <c r="J6" s="40"/>
       <c r="K6" s="40"/>
@@ -18760,7 +18903,7 @@
       <c r="M6" s="40"/>
       <c r="N6" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -18775,14 +18918,16 @@
         <v>1266</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>1421</v>
+        <v>1412</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>1461</v>
+        <v>1018</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
+      <c r="H7" s="40">
+        <v>200</v>
+      </c>
       <c r="I7" s="40"/>
       <c r="J7" s="40"/>
       <c r="K7" s="40"/>
@@ -18790,7 +18935,7 @@
       <c r="M7" s="40"/>
       <c r="N7" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -18805,14 +18950,16 @@
         <v>1267</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>1422</v>
+        <v>1412</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>1189</v>
+        <v>1490</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
+      <c r="H8" s="40">
+        <v>280</v>
+      </c>
       <c r="I8" s="40"/>
       <c r="J8" s="40"/>
       <c r="K8" s="40"/>
@@ -18820,7 +18967,7 @@
       <c r="M8" s="40"/>
       <c r="N8" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -18835,14 +18982,16 @@
         <v>1268</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>1423</v>
+        <v>1412</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>1018</v>
+        <v>1491</v>
       </c>
       <c r="F9" s="44"/>
       <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
+      <c r="H9" s="40">
+        <v>280</v>
+      </c>
       <c r="I9" s="40"/>
       <c r="J9" s="40"/>
       <c r="K9" s="40"/>
@@ -18850,7 +18999,7 @@
       <c r="M9" s="40"/>
       <c r="N9" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -18865,14 +19014,16 @@
         <v>1269</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>1424</v>
+        <v>1412</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>1462</v>
+        <v>1492</v>
       </c>
       <c r="F10" s="44"/>
       <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
+      <c r="H10" s="40">
+        <v>200</v>
+      </c>
       <c r="I10" s="40"/>
       <c r="J10" s="40"/>
       <c r="K10" s="40"/>
@@ -18880,7 +19031,7 @@
       <c r="M10" s="40"/>
       <c r="N10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -18895,14 +19046,16 @@
         <v>1270</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>1425</v>
+        <v>1412</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>1463</v>
+        <v>1493</v>
       </c>
       <c r="F11" s="44"/>
       <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
+      <c r="H11" s="40">
+        <v>200</v>
+      </c>
       <c r="I11" s="40"/>
       <c r="J11" s="40"/>
       <c r="K11" s="40"/>
@@ -18910,7 +19063,7 @@
       <c r="M11" s="40"/>
       <c r="N11" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -18925,14 +19078,16 @@
         <v>1271</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>1425</v>
+        <v>1412</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>1463</v>
+        <v>1494</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="H12" s="40">
+        <v>200</v>
+      </c>
       <c r="I12" s="40"/>
       <c r="J12" s="40"/>
       <c r="K12" s="40"/>
@@ -18940,7 +19095,7 @@
       <c r="M12" s="40"/>
       <c r="N12" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -18955,14 +19110,16 @@
         <v>1272</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>1464</v>
+        <v>1495</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="H13" s="40">
+        <v>280</v>
+      </c>
       <c r="I13" s="40"/>
       <c r="J13" s="40"/>
       <c r="K13" s="40"/>
@@ -18970,7 +19127,7 @@
       <c r="M13" s="40"/>
       <c r="N13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -18985,14 +19142,16 @@
         <v>1273</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>1465</v>
+        <v>1496</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
+      <c r="H14" s="40">
+        <v>280</v>
+      </c>
       <c r="I14" s="40"/>
       <c r="J14" s="40"/>
       <c r="K14" s="40"/>
@@ -19000,7 +19159,7 @@
       <c r="M14" s="40"/>
       <c r="N14" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -19015,14 +19174,16 @@
         <v>1274</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1427</v>
+        <v>1412</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>1466</v>
+        <v>1497</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
+      <c r="H15" s="40">
+        <v>280</v>
+      </c>
       <c r="I15" s="40"/>
       <c r="J15" s="40"/>
       <c r="K15" s="40"/>
@@ -19030,7 +19191,7 @@
       <c r="M15" s="40"/>
       <c r="N15" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -19045,14 +19206,16 @@
         <v>1275</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>1417</v>
+        <v>1448</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
+      <c r="H16" s="40">
+        <v>400</v>
+      </c>
       <c r="I16" s="40"/>
       <c r="J16" s="40"/>
       <c r="K16" s="40"/>
@@ -19060,7 +19223,7 @@
       <c r="M16" s="40"/>
       <c r="N16" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -19075,14 +19238,16 @@
         <v>1276</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>1428</v>
+        <v>1449</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>1467</v>
+        <v>937</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
+      <c r="H17" s="40">
+        <v>360</v>
+      </c>
       <c r="I17" s="40"/>
       <c r="J17" s="40"/>
       <c r="K17" s="40"/>
@@ -19090,7 +19255,7 @@
       <c r="M17" s="40"/>
       <c r="N17" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -19105,14 +19270,16 @@
         <v>1277</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>1468</v>
+        <v>819</v>
       </c>
       <c r="F18" s="44"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
+      <c r="H18" s="40">
+        <v>720</v>
+      </c>
       <c r="I18" s="40"/>
       <c r="J18" s="40"/>
       <c r="K18" s="40"/>
@@ -19120,7 +19287,7 @@
       <c r="M18" s="40"/>
       <c r="N18" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -19135,14 +19302,16 @@
         <v>1278</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>1467</v>
+        <v>1434</v>
       </c>
       <c r="F19" s="44"/>
       <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
+      <c r="H19" s="40">
+        <v>200</v>
+      </c>
       <c r="I19" s="40"/>
       <c r="J19" s="40"/>
       <c r="K19" s="40"/>
@@ -19150,7 +19319,7 @@
       <c r="M19" s="40"/>
       <c r="N19" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -19165,14 +19334,16 @@
         <v>1279</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>1430</v>
+        <v>1417</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>1469</v>
+        <v>1439</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
+      <c r="H20" s="40">
+        <v>510</v>
+      </c>
       <c r="I20" s="40"/>
       <c r="J20" s="40"/>
       <c r="K20" s="40"/>
@@ -19180,7 +19351,7 @@
       <c r="M20" s="40"/>
       <c r="N20" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -19195,14 +19366,16 @@
         <v>1280</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>1431</v>
+        <v>1451</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
+      <c r="H21" s="40">
+        <v>160</v>
+      </c>
       <c r="I21" s="40"/>
       <c r="J21" s="40"/>
       <c r="K21" s="40"/>
@@ -19210,7 +19383,7 @@
       <c r="M21" s="40"/>
       <c r="N21" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -19225,14 +19398,16 @@
         <v>1281</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>1432</v>
+        <v>1416</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>1018</v>
+        <v>1439</v>
       </c>
       <c r="F22" s="44"/>
       <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
+      <c r="H22" s="40">
+        <v>560</v>
+      </c>
       <c r="I22" s="40"/>
       <c r="J22" s="40"/>
       <c r="K22" s="40"/>
@@ -19240,7 +19415,7 @@
       <c r="M22" s="40"/>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>560</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -19255,14 +19430,16 @@
         <v>1282</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>1417</v>
+        <v>1452</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>1488</v>
+        <v>1436</v>
       </c>
       <c r="F23" s="44"/>
       <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
+      <c r="H23" s="40">
+        <v>200</v>
+      </c>
       <c r="I23" s="40"/>
       <c r="J23" s="40"/>
       <c r="K23" s="40"/>
@@ -19270,7 +19447,7 @@
       <c r="M23" s="40"/>
       <c r="N23" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -19285,14 +19462,16 @@
         <v>1283</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>1428</v>
+        <v>1412</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>1125</v>
+        <v>1446</v>
       </c>
       <c r="F24" s="44"/>
       <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
+      <c r="H24" s="40">
+        <v>640</v>
+      </c>
       <c r="I24" s="40"/>
       <c r="J24" s="40"/>
       <c r="K24" s="40"/>
@@ -19300,7 +19479,7 @@
       <c r="M24" s="40"/>
       <c r="N24" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -19315,14 +19494,16 @@
         <v>1284</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>1433</v>
+        <v>1453</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>1470</v>
+        <v>1500</v>
       </c>
       <c r="F25" s="44"/>
       <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
+      <c r="H25" s="40">
+        <v>320</v>
+      </c>
       <c r="I25" s="40"/>
       <c r="J25" s="40"/>
       <c r="K25" s="40"/>
@@ -19330,7 +19511,7 @@
       <c r="M25" s="40"/>
       <c r="N25" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -19345,14 +19526,16 @@
         <v>1285</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>1459</v>
+        <v>1501</v>
       </c>
       <c r="F26" s="44"/>
       <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
+      <c r="H26" s="40">
+        <v>200</v>
+      </c>
       <c r="I26" s="40"/>
       <c r="J26" s="40"/>
       <c r="K26" s="40"/>
@@ -19360,7 +19543,7 @@
       <c r="M26" s="40"/>
       <c r="N26" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
@@ -19375,14 +19558,16 @@
         <v>1286</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>1471</v>
+        <v>1502</v>
       </c>
       <c r="F27" s="44"/>
       <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
+      <c r="H27" s="40">
+        <v>880</v>
+      </c>
       <c r="I27" s="40"/>
       <c r="J27" s="40"/>
       <c r="K27" s="40"/>
@@ -19390,7 +19575,7 @@
       <c r="M27" s="40"/>
       <c r="N27" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>880</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -19405,14 +19590,16 @@
         <v>1287</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>1435</v>
+        <v>1454</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>1490</v>
+        <v>1503</v>
       </c>
       <c r="F28" s="44"/>
       <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
+      <c r="H28" s="40">
+        <v>160</v>
+      </c>
       <c r="I28" s="40"/>
       <c r="J28" s="40"/>
       <c r="K28" s="40"/>
@@ -19420,7 +19607,7 @@
       <c r="M28" s="40"/>
       <c r="N28" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -19435,14 +19622,16 @@
         <v>1288</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>1436</v>
+        <v>1455</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>1480</v>
+        <v>1504</v>
       </c>
       <c r="F29" s="44"/>
       <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
+      <c r="H29" s="40">
+        <v>1200</v>
+      </c>
       <c r="I29" s="40"/>
       <c r="J29" s="40"/>
       <c r="K29" s="40"/>
@@ -19450,7 +19639,7 @@
       <c r="M29" s="40"/>
       <c r="N29" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -19465,14 +19654,16 @@
         <v>1289</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>1437</v>
+        <v>1421</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="F30" s="44"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="H30" s="40">
+        <v>360</v>
+      </c>
       <c r="I30" s="40"/>
       <c r="J30" s="40"/>
       <c r="K30" s="40"/>
@@ -19480,7 +19671,7 @@
       <c r="M30" s="40"/>
       <c r="N30" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -19495,14 +19686,16 @@
         <v>1290</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>1438</v>
+        <v>1456</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>819</v>
+        <v>1505</v>
       </c>
       <c r="F31" s="44"/>
       <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
+      <c r="H31" s="40">
+        <v>160</v>
+      </c>
       <c r="I31" s="40"/>
       <c r="J31" s="40"/>
       <c r="K31" s="40"/>
@@ -19510,7 +19703,7 @@
       <c r="M31" s="40"/>
       <c r="N31" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
@@ -19525,14 +19718,16 @@
         <v>1291</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>1428</v>
+        <v>1412</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>1472</v>
+        <v>1506</v>
       </c>
       <c r="F32" s="44"/>
       <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
+      <c r="H32" s="40">
+        <v>1640</v>
+      </c>
       <c r="I32" s="40"/>
       <c r="J32" s="40"/>
       <c r="K32" s="40"/>
@@ -19540,7 +19735,7 @@
       <c r="M32" s="40"/>
       <c r="N32" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
@@ -19555,14 +19750,16 @@
         <v>1292</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>1439</v>
+        <v>1457</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>1473</v>
+        <v>1125</v>
       </c>
       <c r="F33" s="44"/>
       <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
+      <c r="H33" s="40">
+        <v>160</v>
+      </c>
       <c r="I33" s="40"/>
       <c r="J33" s="40"/>
       <c r="K33" s="40"/>
@@ -19570,7 +19767,7 @@
       <c r="M33" s="40"/>
       <c r="N33" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -19585,14 +19782,16 @@
         <v>1293</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>1440</v>
+        <v>1424</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>1492</v>
+        <v>1507</v>
       </c>
       <c r="F34" s="44"/>
       <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
+      <c r="H34" s="40">
+        <v>2000</v>
+      </c>
       <c r="I34" s="40"/>
       <c r="J34" s="40"/>
       <c r="K34" s="40"/>
@@ -19600,7 +19799,7 @@
       <c r="M34" s="40"/>
       <c r="N34" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
@@ -19615,14 +19814,16 @@
         <v>1294</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>1441</v>
+        <v>1458</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>1474</v>
+        <v>1508</v>
       </c>
       <c r="F35" s="44"/>
       <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
+      <c r="H35" s="40">
+        <v>200</v>
+      </c>
       <c r="I35" s="40"/>
       <c r="J35" s="40"/>
       <c r="K35" s="40"/>
@@ -19630,7 +19831,7 @@
       <c r="M35" s="40"/>
       <c r="N35" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
@@ -19645,14 +19846,16 @@
         <v>1295</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>1442</v>
+        <v>1419</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>1475</v>
+        <v>1509</v>
       </c>
       <c r="F36" s="44"/>
       <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
+      <c r="H36" s="40">
+        <v>1600</v>
+      </c>
       <c r="I36" s="40"/>
       <c r="J36" s="40"/>
       <c r="K36" s="40"/>
@@ -19660,7 +19863,7 @@
       <c r="M36" s="40"/>
       <c r="N36" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -19678,11 +19881,13 @@
         <v>1425</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>1463</v>
+        <v>1510</v>
       </c>
       <c r="F37" s="44"/>
       <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
+      <c r="H37" s="40">
+        <v>280</v>
+      </c>
       <c r="I37" s="40"/>
       <c r="J37" s="40"/>
       <c r="K37" s="40"/>
@@ -19690,7 +19895,7 @@
       <c r="M37" s="40"/>
       <c r="N37" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
@@ -19705,14 +19910,16 @@
         <v>1297</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>1425</v>
+        <v>1459</v>
       </c>
       <c r="E38" s="43" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="F38" s="44"/>
       <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
+      <c r="H38" s="40">
+        <v>200</v>
+      </c>
       <c r="I38" s="40"/>
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
@@ -19720,7 +19927,7 @@
       <c r="M38" s="40"/>
       <c r="N38" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
@@ -19735,14 +19942,16 @@
         <v>1298</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>1425</v>
+        <v>1460</v>
       </c>
       <c r="E39" s="43" t="s">
-        <v>1477</v>
+        <v>1447</v>
       </c>
       <c r="F39" s="44"/>
       <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
+      <c r="H39" s="40">
+        <v>840</v>
+      </c>
       <c r="I39" s="40"/>
       <c r="J39" s="40"/>
       <c r="K39" s="40"/>
@@ -19750,7 +19959,7 @@
       <c r="M39" s="40"/>
       <c r="N39" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>840</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
@@ -19765,14 +19974,16 @@
         <v>1299</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>1432</v>
+        <v>1461</v>
       </c>
       <c r="E40" s="43" t="s">
-        <v>1018</v>
+        <v>819</v>
       </c>
       <c r="F40" s="44"/>
       <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
+      <c r="H40" s="40">
+        <v>320</v>
+      </c>
       <c r="I40" s="40"/>
       <c r="J40" s="40"/>
       <c r="K40" s="40"/>
@@ -19780,7 +19991,7 @@
       <c r="M40" s="40"/>
       <c r="N40" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
@@ -19795,14 +20006,16 @@
         <v>1300</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="E41" s="43" t="s">
-        <v>1460</v>
+        <v>1440</v>
       </c>
       <c r="F41" s="44"/>
       <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
+      <c r="H41" s="40">
+        <v>160</v>
+      </c>
       <c r="I41" s="40"/>
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
@@ -19810,7 +20023,7 @@
       <c r="M41" s="40"/>
       <c r="N41" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
@@ -19825,14 +20038,16 @@
         <v>1301</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>1428</v>
+        <v>1462</v>
       </c>
       <c r="E42" s="43" t="s">
-        <v>1465</v>
+        <v>1512</v>
       </c>
       <c r="F42" s="44"/>
       <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
+      <c r="H42" s="40">
+        <v>160</v>
+      </c>
       <c r="I42" s="40"/>
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
@@ -19840,7 +20055,7 @@
       <c r="M42" s="40"/>
       <c r="N42" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
@@ -19855,14 +20070,16 @@
         <v>1302</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>1424</v>
+        <v>1463</v>
       </c>
       <c r="E43" s="43" t="s">
-        <v>1469</v>
+        <v>1189</v>
       </c>
       <c r="F43" s="44"/>
       <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
+      <c r="H43" s="40">
+        <v>1400</v>
+      </c>
       <c r="I43" s="40"/>
       <c r="J43" s="40"/>
       <c r="K43" s="40"/>
@@ -19870,7 +20087,7 @@
       <c r="M43" s="40"/>
       <c r="N43" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
@@ -19885,14 +20102,16 @@
         <v>1303</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>1424</v>
+        <v>1464</v>
       </c>
       <c r="E44" s="43" t="s">
-        <v>1462</v>
+        <v>1513</v>
       </c>
       <c r="F44" s="44"/>
       <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
+      <c r="H44" s="40">
+        <v>4880</v>
+      </c>
       <c r="I44" s="40"/>
       <c r="J44" s="40"/>
       <c r="K44" s="40"/>
@@ -19900,7 +20119,7 @@
       <c r="M44" s="40"/>
       <c r="N44" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
@@ -19915,14 +20134,16 @@
         <v>1304</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="E45" s="43" t="s">
-        <v>1478</v>
+        <v>1018</v>
       </c>
       <c r="F45" s="44"/>
       <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
+      <c r="H45" s="40">
+        <v>720</v>
+      </c>
       <c r="I45" s="40"/>
       <c r="J45" s="40"/>
       <c r="K45" s="40"/>
@@ -19930,7 +20151,7 @@
       <c r="M45" s="40"/>
       <c r="N45" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
@@ -19945,14 +20166,16 @@
         <v>1305</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>1443</v>
+        <v>1465</v>
       </c>
       <c r="E46" s="43" t="s">
-        <v>1466</v>
+        <v>1442</v>
       </c>
       <c r="F46" s="44"/>
       <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
+      <c r="H46" s="40">
+        <v>400</v>
+      </c>
       <c r="I46" s="40"/>
       <c r="J46" s="40"/>
       <c r="K46" s="40"/>
@@ -19960,7 +20183,7 @@
       <c r="M46" s="40"/>
       <c r="N46" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
@@ -19975,14 +20198,16 @@
         <v>1306</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>1444</v>
+        <v>1418</v>
       </c>
       <c r="E47" s="43" t="s">
-        <v>1479</v>
+        <v>1514</v>
       </c>
       <c r="F47" s="44"/>
       <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
+      <c r="H47" s="40">
+        <v>680</v>
+      </c>
       <c r="I47" s="40"/>
       <c r="J47" s="40"/>
       <c r="K47" s="40"/>
@@ -19990,7 +20215,7 @@
       <c r="M47" s="40"/>
       <c r="N47" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -20005,14 +20230,16 @@
         <v>1307</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>1445</v>
+        <v>1419</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>1480</v>
+        <v>1441</v>
       </c>
       <c r="F48" s="44"/>
       <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
+      <c r="H48" s="40">
+        <v>560</v>
+      </c>
       <c r="I48" s="40"/>
       <c r="J48" s="40"/>
       <c r="K48" s="40"/>
@@ -20020,7 +20247,7 @@
       <c r="M48" s="40"/>
       <c r="N48" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>560</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
@@ -20035,14 +20262,16 @@
         <v>1308</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>1446</v>
+        <v>1413</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>1479</v>
+        <v>937</v>
       </c>
       <c r="F49" s="44"/>
       <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
+      <c r="H49" s="40">
+        <v>480</v>
+      </c>
       <c r="I49" s="40"/>
       <c r="J49" s="40"/>
       <c r="K49" s="40"/>
@@ -20050,7 +20279,7 @@
       <c r="M49" s="40"/>
       <c r="N49" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
@@ -20065,14 +20294,16 @@
         <v>1309</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>1447</v>
+        <v>1466</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>1481</v>
+        <v>1436</v>
       </c>
       <c r="F50" s="44"/>
       <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
+      <c r="H50" s="40">
+        <v>160</v>
+      </c>
       <c r="I50" s="40"/>
       <c r="J50" s="40"/>
       <c r="K50" s="40"/>
@@ -20080,7 +20311,7 @@
       <c r="M50" s="40"/>
       <c r="N50" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
@@ -20095,14 +20326,16 @@
         <v>1310</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>1125</v>
+        <v>1499</v>
       </c>
       <c r="F51" s="44"/>
       <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
+      <c r="H51" s="40">
+        <v>360</v>
+      </c>
       <c r="I51" s="40"/>
       <c r="J51" s="40"/>
       <c r="K51" s="40"/>
@@ -20110,7 +20343,7 @@
       <c r="M51" s="40"/>
       <c r="N51" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
@@ -20125,14 +20358,16 @@
         <v>1311</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>1449</v>
+        <v>1467</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>1492</v>
+        <v>1437</v>
       </c>
       <c r="F52" s="44"/>
       <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
+      <c r="H52" s="40">
+        <v>200</v>
+      </c>
       <c r="I52" s="40"/>
       <c r="J52" s="40"/>
       <c r="K52" s="40"/>
@@ -20140,7 +20375,7 @@
       <c r="M52" s="40"/>
       <c r="N52" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
@@ -20155,14 +20390,16 @@
         <v>1312</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>1450</v>
+        <v>1468</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>1493</v>
+        <v>1515</v>
       </c>
       <c r="F53" s="44"/>
       <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
+      <c r="H53" s="40">
+        <v>320</v>
+      </c>
       <c r="I53" s="40"/>
       <c r="J53" s="40"/>
       <c r="K53" s="40"/>
@@ -20170,7 +20407,7 @@
       <c r="M53" s="40"/>
       <c r="N53" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
@@ -20185,14 +20422,16 @@
         <v>1313</v>
       </c>
       <c r="D54" s="43" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>1236</v>
+        <v>1516</v>
       </c>
       <c r="F54" s="44"/>
       <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
+      <c r="H54" s="40">
+        <v>320</v>
+      </c>
       <c r="I54" s="40"/>
       <c r="J54" s="40"/>
       <c r="K54" s="40"/>
@@ -20200,7 +20439,7 @@
       <c r="M54" s="40"/>
       <c r="N54" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
@@ -20215,14 +20454,16 @@
         <v>1314</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>1419</v>
+        <v>1469</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>1482</v>
+        <v>1515</v>
       </c>
       <c r="F55" s="44"/>
       <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
+      <c r="H55" s="40">
+        <v>800</v>
+      </c>
       <c r="I55" s="40"/>
       <c r="J55" s="40"/>
       <c r="K55" s="40"/>
@@ -20230,7 +20471,7 @@
       <c r="M55" s="40"/>
       <c r="N55" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
@@ -20245,14 +20486,16 @@
         <v>1315</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>1466</v>
+        <v>1517</v>
       </c>
       <c r="F56" s="44"/>
       <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
+      <c r="H56" s="40">
+        <v>160</v>
+      </c>
       <c r="I56" s="40"/>
       <c r="J56" s="40"/>
       <c r="K56" s="40"/>
@@ -20260,7 +20503,7 @@
       <c r="M56" s="40"/>
       <c r="N56" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
@@ -20275,14 +20518,16 @@
         <v>1316</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>1425</v>
+        <v>1538</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>1483</v>
+        <v>1538</v>
       </c>
       <c r="F57" s="44"/>
       <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
+      <c r="H57" s="40">
+        <v>40</v>
+      </c>
       <c r="I57" s="40"/>
       <c r="J57" s="40"/>
       <c r="K57" s="40"/>
@@ -20290,7 +20535,7 @@
       <c r="M57" s="40"/>
       <c r="N57" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
@@ -20305,14 +20550,16 @@
         <v>1317</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>1451</v>
+        <v>1470</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>1466</v>
+        <v>1518</v>
       </c>
       <c r="F58" s="44"/>
       <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
+      <c r="H58" s="40">
+        <v>12179</v>
+      </c>
       <c r="I58" s="40"/>
       <c r="J58" s="40"/>
       <c r="K58" s="40"/>
@@ -20320,7 +20567,7 @@
       <c r="M58" s="40"/>
       <c r="N58" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12179</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
@@ -20335,14 +20582,16 @@
         <v>1318</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>1452</v>
+        <v>1428</v>
       </c>
       <c r="E59" s="45" t="s">
-        <v>1466</v>
+        <v>1125</v>
       </c>
       <c r="F59" s="44"/>
       <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
+      <c r="H59" s="40">
+        <v>200</v>
+      </c>
       <c r="I59" s="40"/>
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
@@ -20350,7 +20599,7 @@
       <c r="M59" s="40"/>
       <c r="N59" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
@@ -20365,14 +20614,16 @@
         <v>1319</v>
       </c>
       <c r="D60" s="43" t="s">
-        <v>1428</v>
+        <v>1419</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>1472</v>
+        <v>1437</v>
       </c>
       <c r="F60" s="44"/>
       <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
+      <c r="H60" s="40">
+        <v>1120</v>
+      </c>
       <c r="I60" s="40"/>
       <c r="J60" s="40"/>
       <c r="K60" s="40"/>
@@ -20380,7 +20631,7 @@
       <c r="M60" s="40"/>
       <c r="N60" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
@@ -20395,14 +20646,16 @@
         <v>1320</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>1484</v>
+        <v>1519</v>
       </c>
       <c r="F61" s="44"/>
       <c r="G61" s="40"/>
-      <c r="H61" s="40"/>
+      <c r="H61" s="40">
+        <v>1760</v>
+      </c>
       <c r="I61" s="40"/>
       <c r="J61" s="40"/>
       <c r="K61" s="40"/>
@@ -20410,7 +20663,7 @@
       <c r="M61" s="40"/>
       <c r="N61" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
@@ -20425,14 +20678,16 @@
         <v>1321</v>
       </c>
       <c r="D62" s="43" t="s">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>1485</v>
+        <v>1520</v>
       </c>
       <c r="F62" s="44"/>
       <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
+      <c r="H62" s="40">
+        <v>1200</v>
+      </c>
       <c r="I62" s="40"/>
       <c r="J62" s="40"/>
       <c r="K62" s="40"/>
@@ -20440,7 +20695,7 @@
       <c r="M62" s="40"/>
       <c r="N62" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
@@ -20455,14 +20710,16 @@
         <v>1322</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>1454</v>
+        <v>1430</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>1494</v>
+        <v>1437</v>
       </c>
       <c r="F63" s="44"/>
       <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
+      <c r="H63" s="40">
+        <v>1000</v>
+      </c>
       <c r="I63" s="40"/>
       <c r="J63" s="40"/>
       <c r="K63" s="40"/>
@@ -20470,7 +20727,7 @@
       <c r="M63" s="40"/>
       <c r="N63" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
@@ -20485,14 +20742,16 @@
         <v>1323</v>
       </c>
       <c r="D64" s="43" t="s">
-        <v>1455</v>
+        <v>1428</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>1018</v>
+        <v>1440</v>
       </c>
       <c r="F64" s="44"/>
       <c r="G64" s="40"/>
-      <c r="H64" s="40"/>
+      <c r="H64" s="40">
+        <v>440</v>
+      </c>
       <c r="I64" s="40"/>
       <c r="J64" s="40"/>
       <c r="K64" s="40"/>
@@ -20500,7 +20759,7 @@
       <c r="M64" s="40"/>
       <c r="N64" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
@@ -20515,14 +20774,16 @@
         <v>1324</v>
       </c>
       <c r="D65" s="43" t="s">
-        <v>1456</v>
+        <v>1413</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>1018</v>
+        <v>1443</v>
       </c>
       <c r="F65" s="44"/>
       <c r="G65" s="40"/>
-      <c r="H65" s="40"/>
+      <c r="H65" s="40">
+        <v>280</v>
+      </c>
       <c r="I65" s="40"/>
       <c r="J65" s="40"/>
       <c r="K65" s="40"/>
@@ -20530,7 +20791,7 @@
       <c r="M65" s="40"/>
       <c r="N65" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
@@ -20545,14 +20806,16 @@
         <v>1325</v>
       </c>
       <c r="D66" s="43" t="s">
-        <v>1431</v>
+        <v>1471</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>1189</v>
+        <v>1236</v>
       </c>
       <c r="F66" s="44"/>
       <c r="G66" s="40"/>
-      <c r="H66" s="40"/>
+      <c r="H66" s="40">
+        <v>200</v>
+      </c>
       <c r="I66" s="40"/>
       <c r="J66" s="40"/>
       <c r="K66" s="40"/>
@@ -20560,7 +20823,7 @@
       <c r="M66" s="40"/>
       <c r="N66" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
@@ -20575,14 +20838,16 @@
         <v>1326</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>1419</v>
+        <v>1431</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>1486</v>
+        <v>1521</v>
       </c>
       <c r="F67" s="44"/>
       <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
+      <c r="H67" s="40">
+        <v>60</v>
+      </c>
       <c r="I67" s="40"/>
       <c r="J67" s="40"/>
       <c r="K67" s="40"/>
@@ -20590,7 +20855,7 @@
       <c r="M67" s="40"/>
       <c r="N67" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
@@ -20605,14 +20870,16 @@
         <v>1327</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>1457</v>
+        <v>1431</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>1468</v>
+        <v>1444</v>
       </c>
       <c r="F68" s="44"/>
       <c r="G68" s="40"/>
-      <c r="H68" s="40"/>
+      <c r="H68" s="40">
+        <v>80</v>
+      </c>
       <c r="I68" s="40"/>
       <c r="J68" s="40"/>
       <c r="K68" s="40"/>
@@ -20620,7 +20887,7 @@
       <c r="M68" s="40"/>
       <c r="N68" s="7">
         <f t="shared" ref="N68:N131" si="2">SUM(G68:M68)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
@@ -20635,14 +20902,16 @@
         <v>1328</v>
       </c>
       <c r="D69" s="43" t="s">
-        <v>1441</v>
+        <v>1432</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>1479</v>
+        <v>1522</v>
       </c>
       <c r="F69" s="44"/>
       <c r="G69" s="40"/>
-      <c r="H69" s="40"/>
+      <c r="H69" s="40">
+        <v>240</v>
+      </c>
       <c r="I69" s="40"/>
       <c r="J69" s="40"/>
       <c r="K69" s="40"/>
@@ -20650,7 +20919,7 @@
       <c r="M69" s="40"/>
       <c r="N69" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
@@ -20665,14 +20934,16 @@
         <v>1329</v>
       </c>
       <c r="D70" s="43" t="s">
-        <v>1425</v>
+        <v>1472</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>1469</v>
+        <v>1018</v>
       </c>
       <c r="F70" s="44"/>
       <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
+      <c r="H70" s="40">
+        <v>160</v>
+      </c>
       <c r="I70" s="40"/>
       <c r="J70" s="40"/>
       <c r="K70" s="40"/>
@@ -20680,7 +20951,7 @@
       <c r="M70" s="40"/>
       <c r="N70" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
@@ -20695,14 +20966,16 @@
         <v>1330</v>
       </c>
       <c r="D71" s="43" t="s">
-        <v>1458</v>
+        <v>1473</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>1495</v>
+        <v>1018</v>
       </c>
       <c r="F71" s="44"/>
       <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
+      <c r="H71" s="40">
+        <v>400</v>
+      </c>
       <c r="I71" s="40"/>
       <c r="J71" s="40"/>
       <c r="K71" s="40"/>
@@ -20710,7 +20983,7 @@
       <c r="M71" s="40"/>
       <c r="N71" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
@@ -20725,14 +20998,16 @@
         <v>1331</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>1437</v>
+        <v>1422</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>1491</v>
+        <v>1189</v>
       </c>
       <c r="F72" s="44"/>
       <c r="G72" s="40"/>
-      <c r="H72" s="40"/>
+      <c r="H72" s="40">
+        <v>720</v>
+      </c>
       <c r="I72" s="40"/>
       <c r="J72" s="40"/>
       <c r="K72" s="40"/>
@@ -20740,7 +21015,7 @@
       <c r="M72" s="40"/>
       <c r="N72" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
@@ -20755,14 +21030,16 @@
         <v>1332</v>
       </c>
       <c r="D73" s="43" t="s">
-        <v>1419</v>
+        <v>1413</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>1459</v>
+        <v>1445</v>
       </c>
       <c r="F73" s="44"/>
       <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
+      <c r="H73" s="40">
+        <v>360</v>
+      </c>
       <c r="I73" s="40"/>
       <c r="J73" s="40"/>
       <c r="K73" s="40"/>
@@ -20770,7 +21047,7 @@
       <c r="M73" s="40"/>
       <c r="N73" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
@@ -20785,14 +21062,16 @@
         <v>1333</v>
       </c>
       <c r="D74" s="43" t="s">
-        <v>1419</v>
+        <v>1474</v>
       </c>
       <c r="E74" s="45" t="s">
-        <v>1460</v>
+        <v>1523</v>
       </c>
       <c r="F74" s="44"/>
       <c r="G74" s="40"/>
-      <c r="H74" s="40"/>
+      <c r="H74" s="40">
+        <v>400</v>
+      </c>
       <c r="I74" s="40"/>
       <c r="J74" s="40"/>
       <c r="K74" s="40"/>
@@ -20800,7 +21079,7 @@
       <c r="M74" s="40"/>
       <c r="N74" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
@@ -20814,11 +21093,17 @@
       <c r="C75" s="44" t="s">
         <v>1334</v>
       </c>
-      <c r="D75" s="43"/>
-      <c r="E75" s="45"/>
+      <c r="D75" s="43" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E75" s="45" t="s">
+        <v>1524</v>
+      </c>
       <c r="F75" s="44"/>
       <c r="G75" s="40"/>
-      <c r="H75" s="40"/>
+      <c r="H75" s="40">
+        <v>1000</v>
+      </c>
       <c r="I75" s="40"/>
       <c r="J75" s="40"/>
       <c r="K75" s="40"/>
@@ -20826,7 +21111,7 @@
       <c r="M75" s="40"/>
       <c r="N75" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
@@ -20840,11 +21125,17 @@
       <c r="C76" s="44" t="s">
         <v>1335</v>
       </c>
-      <c r="D76" s="43"/>
-      <c r="E76" s="45"/>
+      <c r="D76" s="43" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E76" s="45" t="s">
+        <v>1438</v>
+      </c>
       <c r="F76" s="44"/>
       <c r="G76" s="40"/>
-      <c r="H76" s="40"/>
+      <c r="H76" s="40">
+        <v>360</v>
+      </c>
       <c r="I76" s="40"/>
       <c r="J76" s="40"/>
       <c r="K76" s="40"/>
@@ -20852,7 +21143,7 @@
       <c r="M76" s="40"/>
       <c r="N76" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
@@ -20866,11 +21157,17 @@
       <c r="C77" s="44" t="s">
         <v>1336</v>
       </c>
-      <c r="D77" s="43"/>
-      <c r="E77" s="45"/>
+      <c r="D77" s="43" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E77" s="45" t="s">
+        <v>1447</v>
+      </c>
       <c r="F77" s="44"/>
       <c r="G77" s="40"/>
-      <c r="H77" s="40"/>
+      <c r="H77" s="40">
+        <v>200</v>
+      </c>
       <c r="I77" s="40"/>
       <c r="J77" s="40"/>
       <c r="K77" s="40"/>
@@ -20878,7 +21175,7 @@
       <c r="M77" s="40"/>
       <c r="N77" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
@@ -20892,11 +21189,17 @@
       <c r="C78" s="44" t="s">
         <v>1337</v>
       </c>
-      <c r="D78" s="43"/>
-      <c r="E78" s="45"/>
+      <c r="D78" s="43" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E78" s="45" t="s">
+        <v>1447</v>
+      </c>
       <c r="F78" s="44"/>
       <c r="G78" s="40"/>
-      <c r="H78" s="40"/>
+      <c r="H78" s="40">
+        <v>1200</v>
+      </c>
       <c r="I78" s="40"/>
       <c r="J78" s="40"/>
       <c r="K78" s="40"/>
@@ -20904,7 +21207,7 @@
       <c r="M78" s="40"/>
       <c r="N78" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
@@ -20918,11 +21221,17 @@
       <c r="C79" s="44" t="s">
         <v>1338</v>
       </c>
-      <c r="D79" s="43"/>
-      <c r="E79" s="45"/>
+      <c r="D79" s="43" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E79" s="45" t="s">
+        <v>1498</v>
+      </c>
       <c r="F79" s="44"/>
       <c r="G79" s="40"/>
-      <c r="H79" s="40"/>
+      <c r="H79" s="40">
+        <v>320</v>
+      </c>
       <c r="I79" s="40"/>
       <c r="J79" s="40"/>
       <c r="K79" s="40"/>
@@ -20930,7 +21239,7 @@
       <c r="M79" s="40"/>
       <c r="N79" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
@@ -20944,11 +21253,17 @@
       <c r="C80" s="44" t="s">
         <v>1339</v>
       </c>
-      <c r="D80" s="43"/>
-      <c r="E80" s="45"/>
+      <c r="D80" s="43" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E80" s="45" t="s">
+        <v>1525</v>
+      </c>
       <c r="F80" s="44"/>
       <c r="G80" s="40"/>
-      <c r="H80" s="40"/>
+      <c r="H80" s="40">
+        <v>80</v>
+      </c>
       <c r="I80" s="40"/>
       <c r="J80" s="40"/>
       <c r="K80" s="40"/>
@@ -20956,7 +21271,7 @@
       <c r="M80" s="40"/>
       <c r="N80" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
@@ -20970,11 +21285,17 @@
       <c r="C81" s="44" t="s">
         <v>1340</v>
       </c>
-      <c r="D81" s="43"/>
-      <c r="E81" s="45"/>
+      <c r="D81" s="43" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E81" s="45" t="s">
+        <v>1437</v>
+      </c>
       <c r="F81" s="44"/>
       <c r="G81" s="40"/>
-      <c r="H81" s="40"/>
+      <c r="H81" s="40">
+        <v>80</v>
+      </c>
       <c r="I81" s="40"/>
       <c r="J81" s="40"/>
       <c r="K81" s="40"/>
@@ -20982,7 +21303,7 @@
       <c r="M81" s="40"/>
       <c r="N81" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
@@ -20996,11 +21317,17 @@
       <c r="C82" s="44" t="s">
         <v>1341</v>
       </c>
-      <c r="D82" s="43"/>
-      <c r="E82" s="45"/>
+      <c r="D82" s="43" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E82" s="45" t="s">
+        <v>1526</v>
+      </c>
       <c r="F82" s="44"/>
       <c r="G82" s="40"/>
-      <c r="H82" s="40"/>
+      <c r="H82" s="40">
+        <v>236</v>
+      </c>
       <c r="I82" s="40"/>
       <c r="J82" s="40"/>
       <c r="K82" s="40"/>
@@ -21008,7 +21335,7 @@
       <c r="M82" s="40"/>
       <c r="N82" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
@@ -21022,11 +21349,17 @@
       <c r="C83" s="44" t="s">
         <v>1342</v>
       </c>
-      <c r="D83" s="43"/>
-      <c r="E83" s="45"/>
+      <c r="D83" s="43" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E83" s="45" t="s">
+        <v>1527</v>
+      </c>
       <c r="F83" s="44"/>
       <c r="G83" s="40"/>
-      <c r="H83" s="40"/>
+      <c r="H83" s="40">
+        <v>160</v>
+      </c>
       <c r="I83" s="40"/>
       <c r="J83" s="40"/>
       <c r="K83" s="40"/>
@@ -21034,7 +21367,7 @@
       <c r="M83" s="40"/>
       <c r="N83" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
@@ -21048,11 +21381,17 @@
       <c r="C84" s="44" t="s">
         <v>1343</v>
       </c>
-      <c r="D84" s="43"/>
-      <c r="E84" s="45"/>
+      <c r="D84" s="43" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E84" s="45" t="s">
+        <v>1528</v>
+      </c>
       <c r="F84" s="44"/>
       <c r="G84" s="40"/>
-      <c r="H84" s="40"/>
+      <c r="H84" s="40">
+        <v>440</v>
+      </c>
       <c r="I84" s="40"/>
       <c r="J84" s="40"/>
       <c r="K84" s="40"/>
@@ -21060,7 +21399,7 @@
       <c r="M84" s="40"/>
       <c r="N84" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
@@ -21074,11 +21413,17 @@
       <c r="C85" s="44" t="s">
         <v>1344</v>
       </c>
-      <c r="D85" s="43"/>
-      <c r="E85" s="45"/>
+      <c r="D85" s="43" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E85" s="45" t="s">
+        <v>1442</v>
+      </c>
       <c r="F85" s="44"/>
       <c r="G85" s="40"/>
-      <c r="H85" s="40"/>
+      <c r="H85" s="40">
+        <v>240</v>
+      </c>
       <c r="I85" s="40"/>
       <c r="J85" s="40"/>
       <c r="K85" s="40"/>
@@ -21086,7 +21431,7 @@
       <c r="M85" s="40"/>
       <c r="N85" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
@@ -21100,11 +21445,17 @@
       <c r="C86" s="44" t="s">
         <v>1345</v>
       </c>
-      <c r="D86" s="43"/>
-      <c r="E86" s="45"/>
+      <c r="D86" s="43" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E86" s="45" t="s">
+        <v>1441</v>
+      </c>
       <c r="F86" s="44"/>
       <c r="G86" s="40"/>
-      <c r="H86" s="40"/>
+      <c r="H86" s="40">
+        <v>560</v>
+      </c>
       <c r="I86" s="40"/>
       <c r="J86" s="40"/>
       <c r="K86" s="40"/>
@@ -21112,7 +21463,7 @@
       <c r="M86" s="40"/>
       <c r="N86" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>560</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
@@ -21126,11 +21477,17 @@
       <c r="C87" s="44" t="s">
         <v>1346</v>
       </c>
-      <c r="D87" s="43"/>
-      <c r="E87" s="45"/>
+      <c r="D87" s="43" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E87" s="45" t="s">
+        <v>1018</v>
+      </c>
       <c r="F87" s="44"/>
       <c r="G87" s="40"/>
-      <c r="H87" s="40"/>
+      <c r="H87" s="40">
+        <v>920</v>
+      </c>
       <c r="I87" s="40"/>
       <c r="J87" s="40"/>
       <c r="K87" s="40"/>
@@ -21138,7 +21495,7 @@
       <c r="M87" s="40"/>
       <c r="N87" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>920</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
@@ -21152,11 +21509,17 @@
       <c r="C88" s="44" t="s">
         <v>1347</v>
       </c>
-      <c r="D88" s="43"/>
-      <c r="E88" s="45"/>
+      <c r="D88" s="43" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E88" s="45" t="s">
+        <v>1518</v>
+      </c>
       <c r="F88" s="44"/>
       <c r="G88" s="40"/>
-      <c r="H88" s="40"/>
+      <c r="H88" s="40">
+        <v>7600</v>
+      </c>
       <c r="I88" s="40"/>
       <c r="J88" s="40"/>
       <c r="K88" s="40"/>
@@ -21164,7 +21527,7 @@
       <c r="M88" s="40"/>
       <c r="N88" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
@@ -21178,11 +21541,17 @@
       <c r="C89" s="44" t="s">
         <v>1348</v>
       </c>
-      <c r="D89" s="43"/>
-      <c r="E89" s="45"/>
+      <c r="D89" s="43" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E89" s="45" t="s">
+        <v>1018</v>
+      </c>
       <c r="F89" s="44"/>
       <c r="G89" s="40"/>
-      <c r="H89" s="40"/>
+      <c r="H89" s="40">
+        <v>9600</v>
+      </c>
       <c r="I89" s="40"/>
       <c r="J89" s="40"/>
       <c r="K89" s="40"/>
@@ -21190,7 +21559,7 @@
       <c r="M89" s="40"/>
       <c r="N89" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
@@ -21204,11 +21573,17 @@
       <c r="C90" s="44" t="s">
         <v>1349</v>
       </c>
-      <c r="D90" s="43"/>
-      <c r="E90" s="45"/>
+      <c r="D90" s="43" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E90" s="45" t="s">
+        <v>1018</v>
+      </c>
       <c r="F90" s="44"/>
       <c r="G90" s="40"/>
-      <c r="H90" s="40"/>
+      <c r="H90" s="40">
+        <v>1760</v>
+      </c>
       <c r="I90" s="40"/>
       <c r="J90" s="40"/>
       <c r="K90" s="40"/>
@@ -21216,7 +21591,7 @@
       <c r="M90" s="40"/>
       <c r="N90" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
@@ -21230,11 +21605,17 @@
       <c r="C91" s="44" t="s">
         <v>1350</v>
       </c>
-      <c r="D91" s="43"/>
-      <c r="E91" s="45"/>
+      <c r="D91" s="43" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E91" s="45" t="s">
+        <v>1435</v>
+      </c>
       <c r="F91" s="44"/>
       <c r="G91" s="40"/>
-      <c r="H91" s="40"/>
+      <c r="H91" s="40">
+        <v>240</v>
+      </c>
       <c r="I91" s="40"/>
       <c r="J91" s="40"/>
       <c r="K91" s="40"/>
@@ -21242,7 +21623,7 @@
       <c r="M91" s="40"/>
       <c r="N91" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
@@ -21256,11 +21637,17 @@
       <c r="C92" s="44" t="s">
         <v>1351</v>
       </c>
-      <c r="D92" s="43"/>
-      <c r="E92" s="45"/>
+      <c r="D92" s="43" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E92" s="45" t="s">
+        <v>1529</v>
+      </c>
       <c r="F92" s="44"/>
       <c r="G92" s="40"/>
-      <c r="H92" s="40"/>
+      <c r="H92" s="40">
+        <v>360</v>
+      </c>
       <c r="I92" s="40"/>
       <c r="J92" s="40"/>
       <c r="K92" s="40"/>
@@ -21268,7 +21655,7 @@
       <c r="M92" s="40"/>
       <c r="N92" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
@@ -21282,11 +21669,17 @@
       <c r="C93" s="44" t="s">
         <v>1352</v>
       </c>
-      <c r="D93" s="43"/>
-      <c r="E93" s="45"/>
+      <c r="D93" s="43" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E93" s="45" t="s">
+        <v>1125</v>
+      </c>
       <c r="F93" s="44"/>
       <c r="G93" s="40"/>
-      <c r="H93" s="40"/>
+      <c r="H93" s="40">
+        <v>240</v>
+      </c>
       <c r="I93" s="40"/>
       <c r="J93" s="40"/>
       <c r="K93" s="40"/>
@@ -21294,7 +21687,7 @@
       <c r="M93" s="40"/>
       <c r="N93" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
@@ -21308,11 +21701,17 @@
       <c r="C94" s="44" t="s">
         <v>1353</v>
       </c>
-      <c r="D94" s="43"/>
-      <c r="E94" s="45"/>
+      <c r="D94" s="43" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E94" s="45" t="s">
+        <v>1530</v>
+      </c>
       <c r="F94" s="44"/>
       <c r="G94" s="40"/>
-      <c r="H94" s="40"/>
+      <c r="H94" s="40">
+        <v>314</v>
+      </c>
       <c r="I94" s="40"/>
       <c r="J94" s="40"/>
       <c r="K94" s="40"/>
@@ -21320,7 +21719,7 @@
       <c r="M94" s="40"/>
       <c r="N94" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
@@ -21334,11 +21733,17 @@
       <c r="C95" s="44" t="s">
         <v>1354</v>
       </c>
-      <c r="D95" s="43"/>
-      <c r="E95" s="45"/>
+      <c r="D95" s="43" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E95" s="45" t="s">
+        <v>1443</v>
+      </c>
       <c r="F95" s="44"/>
       <c r="G95" s="40"/>
-      <c r="H95" s="40"/>
+      <c r="H95" s="40">
+        <v>120</v>
+      </c>
       <c r="I95" s="40"/>
       <c r="J95" s="40"/>
       <c r="K95" s="40"/>
@@ -21346,7 +21751,7 @@
       <c r="M95" s="40"/>
       <c r="N95" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
@@ -21360,11 +21765,17 @@
       <c r="C96" s="44" t="s">
         <v>1355</v>
       </c>
-      <c r="D96" s="43"/>
-      <c r="E96" s="45"/>
+      <c r="D96" s="43" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E96" s="45" t="s">
+        <v>1531</v>
+      </c>
       <c r="F96" s="44"/>
       <c r="G96" s="40"/>
-      <c r="H96" s="40"/>
+      <c r="H96" s="40">
+        <v>320</v>
+      </c>
       <c r="I96" s="40"/>
       <c r="J96" s="40"/>
       <c r="K96" s="40"/>
@@ -21372,7 +21783,7 @@
       <c r="M96" s="40"/>
       <c r="N96" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.35">
@@ -21386,11 +21797,17 @@
       <c r="C97" s="44" t="s">
         <v>1356</v>
       </c>
-      <c r="D97" s="43"/>
-      <c r="E97" s="45"/>
+      <c r="D97" s="43" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E97" s="45" t="s">
+        <v>1433</v>
+      </c>
       <c r="F97" s="44"/>
       <c r="G97" s="40"/>
-      <c r="H97" s="40"/>
+      <c r="H97" s="40">
+        <v>360</v>
+      </c>
       <c r="I97" s="40"/>
       <c r="J97" s="40"/>
       <c r="K97" s="40"/>
@@ -21398,7 +21815,7 @@
       <c r="M97" s="40"/>
       <c r="N97" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
@@ -21412,11 +21829,17 @@
       <c r="C98" s="44" t="s">
         <v>1357</v>
       </c>
-      <c r="D98" s="43"/>
-      <c r="E98" s="45"/>
+      <c r="D98" s="43" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E98" s="45" t="s">
+        <v>1532</v>
+      </c>
       <c r="F98" s="44"/>
       <c r="G98" s="40"/>
-      <c r="H98" s="40"/>
+      <c r="H98" s="40">
+        <v>360</v>
+      </c>
       <c r="I98" s="40"/>
       <c r="J98" s="40"/>
       <c r="K98" s="40"/>
@@ -21424,7 +21847,7 @@
       <c r="M98" s="40"/>
       <c r="N98" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.35">
@@ -21438,11 +21861,17 @@
       <c r="C99" s="44" t="s">
         <v>1358</v>
       </c>
-      <c r="D99" s="43"/>
-      <c r="E99" s="45"/>
+      <c r="D99" s="43" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E99" s="45" t="s">
+        <v>1533</v>
+      </c>
       <c r="F99" s="44"/>
       <c r="G99" s="40"/>
-      <c r="H99" s="40"/>
+      <c r="H99" s="40">
+        <v>46</v>
+      </c>
       <c r="I99" s="40"/>
       <c r="J99" s="40"/>
       <c r="K99" s="40"/>
@@ -21450,7 +21879,7 @@
       <c r="M99" s="40"/>
       <c r="N99" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.35">
@@ -21464,11 +21893,17 @@
       <c r="C100" s="44" t="s">
         <v>1359</v>
       </c>
-      <c r="D100" s="43"/>
-      <c r="E100" s="45"/>
+      <c r="D100" s="43" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E100" s="45" t="s">
+        <v>1518</v>
+      </c>
       <c r="F100" s="44"/>
       <c r="G100" s="40"/>
-      <c r="H100" s="40"/>
+      <c r="H100" s="40">
+        <v>2400</v>
+      </c>
       <c r="I100" s="40"/>
       <c r="J100" s="40"/>
       <c r="K100" s="40"/>
@@ -21476,7 +21911,7 @@
       <c r="M100" s="40"/>
       <c r="N100" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
@@ -21490,11 +21925,17 @@
       <c r="C101" s="44" t="s">
         <v>1360</v>
       </c>
-      <c r="D101" s="43"/>
-      <c r="E101" s="45"/>
+      <c r="D101" s="43" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E101" s="45" t="s">
+        <v>1534</v>
+      </c>
       <c r="F101" s="44"/>
       <c r="G101" s="40"/>
-      <c r="H101" s="40"/>
+      <c r="H101" s="40">
+        <v>2000</v>
+      </c>
       <c r="I101" s="40"/>
       <c r="J101" s="40"/>
       <c r="K101" s="40"/>
@@ -21502,7 +21943,7 @@
       <c r="M101" s="40"/>
       <c r="N101" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
@@ -21513,9 +21954,7 @@
       <c r="B102" s="44">
         <v>4</v>
       </c>
-      <c r="C102" s="44" t="s">
-        <v>1361</v>
-      </c>
+      <c r="C102" s="44"/>
       <c r="D102" s="43"/>
       <c r="E102" s="45"/>
       <c r="F102" s="44"/>
@@ -21536,17 +21975,20 @@
         <f t="shared" si="3"/>
         <v>101</v>
       </c>
-      <c r="B103" s="44">
-        <v>4</v>
+      <c r="B103" s="44" t="s">
+        <v>1536</v>
       </c>
       <c r="C103" s="44" t="s">
-        <v>1362</v>
+        <v>1535</v>
       </c>
       <c r="D103" s="43"/>
       <c r="E103" s="45"/>
       <c r="F103" s="44"/>
       <c r="G103" s="40"/>
-      <c r="H103" s="40"/>
+      <c r="H103" s="55">
+        <f>SUM(H3:H101)</f>
+        <v>82065</v>
+      </c>
       <c r="I103" s="40"/>
       <c r="J103" s="40"/>
       <c r="K103" s="40"/>
@@ -21554,7 +21996,7 @@
       <c r="M103" s="40"/>
       <c r="N103" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>82065</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
@@ -21562,17 +22004,20 @@
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="B104" s="44">
-        <v>4</v>
+      <c r="B104" s="44" t="s">
+        <v>1537</v>
       </c>
       <c r="C104" s="44" t="s">
-        <v>1363</v>
+        <v>1535</v>
       </c>
       <c r="D104" s="43"/>
       <c r="E104" s="45"/>
       <c r="F104" s="44"/>
       <c r="G104" s="40"/>
-      <c r="H104" s="40"/>
+      <c r="H104" s="56">
+        <f>H103/40</f>
+        <v>2051.625</v>
+      </c>
       <c r="I104" s="40"/>
       <c r="J104" s="40"/>
       <c r="K104" s="40"/>
@@ -21580,7 +22025,7 @@
       <c r="M104" s="40"/>
       <c r="N104" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2051.625</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
@@ -21591,9 +22036,7 @@
       <c r="B105" s="44">
         <v>4</v>
       </c>
-      <c r="C105" s="44" t="s">
-        <v>1364</v>
-      </c>
+      <c r="C105" s="44"/>
       <c r="D105" s="43"/>
       <c r="E105" s="45"/>
       <c r="F105" s="44"/>
@@ -21617,9 +22060,7 @@
       <c r="B106" s="44">
         <v>4</v>
       </c>
-      <c r="C106" s="44" t="s">
-        <v>1365</v>
-      </c>
+      <c r="C106" s="44"/>
       <c r="D106" s="43"/>
       <c r="E106" s="45"/>
       <c r="F106" s="44"/>
@@ -21644,7 +22085,7 @@
         <v>4</v>
       </c>
       <c r="C107" s="44" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="D107" s="43"/>
       <c r="E107" s="45"/>
@@ -21670,7 +22111,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="44" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="D108" s="43"/>
       <c r="E108" s="43"/>
@@ -21696,7 +22137,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="44" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="D109" s="43"/>
       <c r="E109" s="43"/>
@@ -21722,7 +22163,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="44" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="D110" s="43"/>
       <c r="E110" s="43"/>
@@ -21748,7 +22189,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="44" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="D111" s="43"/>
       <c r="E111" s="43"/>
@@ -21774,7 +22215,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="44" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="D112" s="43"/>
       <c r="E112" s="43"/>
@@ -21800,7 +22241,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="44" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="D113" s="43"/>
       <c r="E113" s="43"/>
@@ -21826,7 +22267,7 @@
         <v>5</v>
       </c>
       <c r="C114" s="44" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="D114" s="43"/>
       <c r="E114" s="43"/>
@@ -21852,7 +22293,7 @@
         <v>5</v>
       </c>
       <c r="C115" s="44" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="D115" s="43"/>
       <c r="E115" s="43"/>
@@ -21878,7 +22319,7 @@
         <v>5</v>
       </c>
       <c r="C116" s="44" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="D116" s="43"/>
       <c r="E116" s="43"/>
@@ -21904,7 +22345,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="44" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="D117" s="43"/>
       <c r="E117" s="43"/>
@@ -21930,7 +22371,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="44" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="D118" s="43"/>
       <c r="E118" s="43"/>
@@ -21956,7 +22397,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="44" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="D119" s="43"/>
       <c r="E119" s="43"/>
@@ -21982,7 +22423,7 @@
         <v>5</v>
       </c>
       <c r="C120" s="44" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="D120" s="43"/>
       <c r="E120" s="43"/>
@@ -22008,7 +22449,7 @@
         <v>5</v>
       </c>
       <c r="C121" s="44" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="D121" s="43"/>
       <c r="E121" s="43"/>
@@ -22034,7 +22475,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="44" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="D122" s="43"/>
       <c r="E122" s="43"/>
@@ -22060,7 +22501,7 @@
         <v>5</v>
       </c>
       <c r="C123" s="44" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="D123" s="43"/>
       <c r="E123" s="43"/>
@@ -22086,7 +22527,7 @@
         <v>5</v>
       </c>
       <c r="C124" s="44" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="D124" s="43"/>
       <c r="E124" s="43"/>
@@ -22112,7 +22553,7 @@
         <v>5</v>
       </c>
       <c r="C125" s="44" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="D125" s="43"/>
       <c r="E125" s="43"/>
@@ -22138,7 +22579,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="44" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="D126" s="43"/>
       <c r="E126" s="43"/>
@@ -22164,7 +22605,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="44" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="D127" s="43"/>
       <c r="E127" s="43"/>
@@ -22190,7 +22631,7 @@
         <v>5</v>
       </c>
       <c r="C128" s="44" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="D128" s="43"/>
       <c r="E128" s="43"/>
@@ -22216,7 +22657,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="44" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="D129" s="43"/>
       <c r="E129" s="43"/>
@@ -22242,7 +22683,7 @@
         <v>5</v>
       </c>
       <c r="C130" s="44" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="D130" s="43"/>
       <c r="E130" s="43"/>
@@ -22268,7 +22709,7 @@
         <v>5</v>
       </c>
       <c r="C131" s="44" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="D131" s="43"/>
       <c r="E131" s="43"/>
@@ -22294,7 +22735,7 @@
         <v>5</v>
       </c>
       <c r="C132" s="44" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D132" s="43"/>
       <c r="E132" s="43"/>
@@ -22320,7 +22761,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="44" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="D133" s="43"/>
       <c r="E133" s="43"/>
@@ -22346,7 +22787,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="44" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="D134" s="43"/>
       <c r="E134" s="43"/>
@@ -22372,7 +22813,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="44" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="D135" s="43"/>
       <c r="E135" s="43"/>
@@ -22398,7 +22839,7 @@
         <v>5</v>
       </c>
       <c r="C136" s="44" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="D136" s="43"/>
       <c r="E136" s="43"/>
@@ -22424,7 +22865,7 @@
         <v>5</v>
       </c>
       <c r="C137" s="44" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="D137" s="43"/>
       <c r="E137" s="43"/>
@@ -22450,7 +22891,7 @@
         <v>5</v>
       </c>
       <c r="C138" s="44" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="D138" s="43"/>
       <c r="E138" s="43"/>
@@ -22476,7 +22917,7 @@
         <v>5</v>
       </c>
       <c r="C139" s="44" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="D139" s="43"/>
       <c r="E139" s="43"/>
@@ -22502,7 +22943,7 @@
         <v>6</v>
       </c>
       <c r="C140" s="44" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="D140" s="43"/>
       <c r="E140" s="45"/>
@@ -22528,7 +22969,7 @@
         <v>6</v>
       </c>
       <c r="C141" s="44" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="D141" s="43"/>
       <c r="E141" s="43"/>
@@ -22554,7 +22995,7 @@
         <v>6</v>
       </c>
       <c r="C142" s="44" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="D142" s="43"/>
       <c r="E142" s="43"/>
@@ -22580,7 +23021,7 @@
         <v>6</v>
       </c>
       <c r="C143" s="44" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="D143" s="43"/>
       <c r="E143" s="43"/>
@@ -22606,7 +23047,7 @@
         <v>6</v>
       </c>
       <c r="C144" s="44" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="D144" s="43"/>
       <c r="E144" s="43"/>
@@ -22632,7 +23073,7 @@
         <v>6</v>
       </c>
       <c r="C145" s="44" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="D145" s="43"/>
       <c r="E145" s="43"/>
@@ -22658,7 +23099,7 @@
         <v>6</v>
       </c>
       <c r="C146" s="44" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="D146" s="43"/>
       <c r="E146" s="43"/>
@@ -22684,7 +23125,7 @@
         <v>6</v>
       </c>
       <c r="C147" s="44" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="D147" s="43"/>
       <c r="E147" s="43"/>
@@ -22710,7 +23151,7 @@
         <v>6</v>
       </c>
       <c r="C148" s="44" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="D148" s="43"/>
       <c r="E148" s="43"/>
@@ -22736,7 +23177,7 @@
         <v>6</v>
       </c>
       <c r="C149" s="44" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="D149" s="43"/>
       <c r="E149" s="43"/>
@@ -22762,7 +23203,7 @@
         <v>6</v>
       </c>
       <c r="C150" s="44" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="D150" s="43"/>
       <c r="E150" s="43"/>
@@ -22788,7 +23229,7 @@
         <v>6</v>
       </c>
       <c r="C151" s="44" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="D151" s="43"/>
       <c r="E151" s="43"/>
@@ -22814,7 +23255,7 @@
         <v>6</v>
       </c>
       <c r="C152" s="44" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="D152" s="43"/>
       <c r="E152" s="43"/>
@@ -22840,7 +23281,7 @@
         <v>6</v>
       </c>
       <c r="C153" s="44" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="D153" s="43"/>
       <c r="E153" s="43"/>
@@ -22866,7 +23307,7 @@
         <v>6</v>
       </c>
       <c r="C154" s="44" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="D154" s="43"/>
       <c r="E154" s="43"/>
@@ -22892,7 +23333,7 @@
         <v>6</v>
       </c>
       <c r="C155" s="44" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="D155" s="43"/>
       <c r="E155" s="43"/>
@@ -22918,7 +23359,7 @@
         <v>6</v>
       </c>
       <c r="C156" s="44" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="D156" s="43"/>
       <c r="E156" s="43"/>
@@ -22944,7 +23385,7 @@
         <v>6</v>
       </c>
       <c r="C157" s="44" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="D157" s="43"/>
       <c r="E157" s="43"/>
@@ -22988,7 +23429,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="80" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="45" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
